--- a/src/test/resources/Data/PlayGround.xlsx
+++ b/src/test/resources/Data/PlayGround.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26F88FD-2AD0-4D80-9ECF-B8BA87090887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CAD94D-CB28-411E-BFCD-CE6084C03D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,6 @@
     <t>Feature</t>
   </si>
   <si>
-    <t>Scenario</t>
-  </si>
-  <si>
     <t>Steps</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>TC_001_Verify Title of Page</t>
+  </si>
+  <si>
+    <t>ScenarioName</t>
   </si>
 </sst>
 </file>
@@ -505,91 +505,91 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>20</v>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>21</v>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>22</v>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
